--- a/data/VINCI-Environment-Day-otazky.xlsx
+++ b/data/VINCI-Environment-Day-otazky.xlsx
@@ -418,7 +418,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1. List OTÁZKY obsahuje 30 řádků – jeden řádek = jedna otázka.</v>
+        <v>1. List OTÁZKY obsahuje 20 řádků – jeden řádek = jedna otázka.</v>
       </c>
     </row>
     <row r="5">
@@ -468,7 +468,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>• Čísla otázek 1–30 neměňte – odpovídají číslům vytištěným na QR plakátech.</v>
+        <v>• Čísla otázek 1–20 neměňte – odpovídají číslům vytištěným na QR plakátech.</v>
       </c>
     </row>
     <row r="15">
@@ -550,7 +550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD32"/>
+  <dimension ref="A1:AD22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1017,2489 +1017,1569 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>Jak dlouho trvá, než se v přírodě rozloží hliníková plechovka od nápoje?</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>200 let</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>50 let</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>500 let</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>Ako dlho trvá, kým sa v prírode rozloží hliníková plechovka od nápoja?</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>200 rokov</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>50 rokov</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>500 rokov</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>Ile czasu zajmuje rozkład aluminiowej puszki po napoju w przyrodzie?</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>200 lat</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>50 lat</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>500 lat</v>
       </c>
       <c r="O6" t="str">
-        <v/>
+        <v>Mennyi idő alatt bomlik le a természetben egy alumínium üdítős doboz?</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>200 év</v>
       </c>
       <c r="Q6" t="str">
-        <v/>
+        <v>50 év</v>
       </c>
       <c r="R6" t="str">
-        <v/>
+        <v>500 év</v>
       </c>
       <c r="S6" t="str">
-        <v/>
+        <v>Cât timp durează până când o cutie de aluminiu pentru băuturi se descompune în natură?</v>
       </c>
       <c r="T6" t="str">
-        <v/>
+        <v>200 de ani</v>
       </c>
       <c r="U6" t="str">
-        <v/>
+        <v>50 de ani</v>
       </c>
       <c r="V6" t="str">
-        <v/>
+        <v>500 de ani</v>
       </c>
       <c r="W6" t="str">
-        <v/>
+        <v>Колко време отнема разграждането на алуминиева кутия от напитка в природата?</v>
       </c>
       <c r="X6" t="str">
-        <v/>
+        <v>200 години</v>
       </c>
       <c r="Y6" t="str">
-        <v/>
+        <v>50 години</v>
       </c>
       <c r="Z6" t="str">
-        <v/>
+        <v>500 години</v>
       </c>
       <c r="AA6" t="str">
-        <v/>
+        <v>How long does it take an aluminium drink can to decompose in nature?</v>
       </c>
       <c r="AB6" t="str">
-        <v/>
+        <v>200 years</v>
       </c>
       <c r="AC6" t="str">
-        <v/>
+        <v>50 years</v>
       </c>
       <c r="AD6" t="str">
-        <v/>
+        <v>500 years</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>Kolik procent domovního odpadu lze v průměru recyklovat?</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>10 %</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>30 %</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>60 %</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>Koľko percent domového odpadu sa dá v priemere recyklovať?</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>10 %</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>30 %</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>60 %</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>Ile procent odpadów domowych można średnio poddać recyklingowi?</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>10%</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>30%</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>60%</v>
       </c>
       <c r="O7" t="str">
-        <v/>
+        <v>A háztartási hulladék hány százaléka újrahasznosítható átlagosan?</v>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>10%</v>
       </c>
       <c r="Q7" t="str">
-        <v/>
+        <v>30%</v>
       </c>
       <c r="R7" t="str">
-        <v/>
+        <v>60%</v>
       </c>
       <c r="S7" t="str">
-        <v/>
+        <v>Ce procent din deșeurile menajere poate fi reciclat, în medie?</v>
       </c>
       <c r="T7" t="str">
-        <v/>
+        <v>10%</v>
       </c>
       <c r="U7" t="str">
-        <v/>
+        <v>30%</v>
       </c>
       <c r="V7" t="str">
-        <v/>
+        <v>60%</v>
       </c>
       <c r="W7" t="str">
-        <v/>
+        <v>Какъв процент от битовите отпадъци обикновено могат да бъдат рециклирани?</v>
       </c>
       <c r="X7" t="str">
-        <v/>
+        <v>10%</v>
       </c>
       <c r="Y7" t="str">
-        <v/>
+        <v>30%</v>
       </c>
       <c r="Z7" t="str">
-        <v/>
+        <v>60%</v>
       </c>
       <c r="AA7" t="str">
-        <v/>
+        <v>What percentage of household waste can typically be recycled?</v>
       </c>
       <c r="AB7" t="str">
-        <v/>
+        <v>10%</v>
       </c>
       <c r="AC7" t="str">
-        <v/>
+        <v>30%</v>
       </c>
       <c r="AD7" t="str">
-        <v/>
+        <v>60%</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>Jak dlouho trvá, než se v přírodě rozloží bavlněné tričko?</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>pár týdnů</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>50 let</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>5 měsíců</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>Ako dlho trvá, kým sa v prírode rozloží bavlnené tričko?</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>pár týždňov</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>50 rokov</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>5 mesiacov</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>Ile czasu zajmuje rozkład bawełnianej koszulki w przyrodzie?</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>kilka tygodni</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>50 lat</v>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>5 miesięcy</v>
       </c>
       <c r="O8" t="str">
-        <v/>
+        <v>Mennyi idő alatt bomlik le a természetben egy pamut póló?</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>néhány hét</v>
       </c>
       <c r="Q8" t="str">
-        <v/>
+        <v>50 év</v>
       </c>
       <c r="R8" t="str">
-        <v/>
+        <v>5 hónap</v>
       </c>
       <c r="S8" t="str">
-        <v/>
+        <v>Cât timp durează până când un tricou din bumbac se descompune în natură?</v>
       </c>
       <c r="T8" t="str">
-        <v/>
+        <v>câteva săptămâni</v>
       </c>
       <c r="U8" t="str">
-        <v/>
+        <v>50 de ani</v>
       </c>
       <c r="V8" t="str">
-        <v/>
+        <v>5 luni</v>
       </c>
       <c r="W8" t="str">
-        <v/>
+        <v>Колко време отнема разграждането на памучна тениска в природата?</v>
       </c>
       <c r="X8" t="str">
-        <v/>
+        <v>няколко седмици</v>
       </c>
       <c r="Y8" t="str">
-        <v/>
+        <v>50 години</v>
       </c>
       <c r="Z8" t="str">
-        <v/>
+        <v>5 месеца</v>
       </c>
       <c r="AA8" t="str">
-        <v/>
+        <v>How long does it take a cotton T-shirt to decompose in nature?</v>
       </c>
       <c r="AB8" t="str">
-        <v/>
+        <v>a few weeks</v>
       </c>
       <c r="AC8" t="str">
-        <v/>
+        <v>50 years</v>
       </c>
       <c r="AD8" t="str">
-        <v/>
+        <v>5 months</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" t="str">
-        <v/>
+      <c r="B9">
+        <v>1</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>Kolik litrů vody je v průměru potřeba na výrobu jednoho bavlněného trička?</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>2 700 l</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>200 l</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>10 000 l</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>Koľko litrov vody je v priemere potrebných na výrobu jedného bavlneného trička?</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>2 700 l</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>200 l</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>10 000 l</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>Ile litrów wody potrzeba średnio do wyprodukowania jednej bawełnianej koszulki?</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>2700 l</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>200 l</v>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>10 000 l</v>
       </c>
       <c r="O9" t="str">
-        <v/>
+        <v>Átlagosan hány liter víz szükséges egy pamut póló elkészítéséhez?</v>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>2700 liter</v>
       </c>
       <c r="Q9" t="str">
-        <v/>
+        <v>200 liter</v>
       </c>
       <c r="R9" t="str">
-        <v/>
+        <v>10 000 liter</v>
       </c>
       <c r="S9" t="str">
-        <v/>
+        <v>Câți litri de apă sunt necesari, în medie, pentru a produce un tricou din bumbac?</v>
       </c>
       <c r="T9" t="str">
-        <v/>
+        <v>2.700 l</v>
       </c>
       <c r="U9" t="str">
-        <v/>
+        <v>200 l</v>
       </c>
       <c r="V9" t="str">
-        <v/>
+        <v>10.000 l</v>
       </c>
       <c r="W9" t="str">
-        <v/>
+        <v>Средно колко литра вода са нужни за производството на една памучна тениска?</v>
       </c>
       <c r="X9" t="str">
-        <v/>
+        <v>2700 л</v>
       </c>
       <c r="Y9" t="str">
-        <v/>
+        <v>200 л</v>
       </c>
       <c r="Z9" t="str">
-        <v/>
+        <v>10 000 л</v>
       </c>
       <c r="AA9" t="str">
-        <v/>
+        <v>How many litres of water does it typically take to make one cotton T-shirt?</v>
       </c>
       <c r="AB9" t="str">
-        <v/>
+        <v>2,700 l</v>
       </c>
       <c r="AC9" t="str">
-        <v/>
+        <v>200 l</v>
       </c>
       <c r="AD9" t="str">
-        <v/>
+        <v>10,000 l</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" t="str">
-        <v/>
+      <c r="B10">
+        <v>2</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>O kolik stupňů Celsia se v průměru oteplila Země od průmyslové revoluce?</v>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>o cca 0,3 °C</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>o cca 1,1 °C</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>o cca 3 °C</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>O koľko stupňov Celzia sa v priemere oteplila Zem od priemyselnej revolúcie?</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>asi o 0,3 °C</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>asi o 1,1 °C</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>asi o 3 °C</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>O ile stopni Celsjusza średnio ociepliła się Ziemia od rewolucji przemysłowej?</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>o ok. 0,3°C</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>o ok. 1,1°C</v>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>o ok. 3°C</v>
       </c>
       <c r="O10" t="str">
-        <v/>
+        <v>Hozzávetőlegesen hány Celsius-fokot melegedett a Föld az ipari forradalom óta?</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>kb. 0,3 °C-ot</v>
       </c>
       <c r="Q10" t="str">
-        <v/>
+        <v>kb. 1,1 °C-ot</v>
       </c>
       <c r="R10" t="str">
-        <v/>
+        <v>kb. 3 °C-ot</v>
       </c>
       <c r="S10" t="str">
-        <v/>
+        <v>Cu aproximativ câte grade Celsius s-a încălzit Pământul de la revoluția industrială?</v>
       </c>
       <c r="T10" t="str">
-        <v/>
+        <v>cu aprox. 0,3°C</v>
       </c>
       <c r="U10" t="str">
-        <v/>
+        <v>cu aprox. 1,1°C</v>
       </c>
       <c r="V10" t="str">
-        <v/>
+        <v>cu aprox. 3°C</v>
       </c>
       <c r="W10" t="str">
-        <v/>
+        <v>Приблизително с колко градуса по Целзий се е затоплила Земята от индустриалната революция насам?</v>
       </c>
       <c r="X10" t="str">
-        <v/>
+        <v>с около 0,3°C</v>
       </c>
       <c r="Y10" t="str">
-        <v/>
+        <v>с около 1,1°C</v>
       </c>
       <c r="Z10" t="str">
-        <v/>
+        <v>с около 3°C</v>
       </c>
       <c r="AA10" t="str">
-        <v/>
+        <v>By roughly how many degrees Celsius has the Earth warmed since the industrial revolution?</v>
       </c>
       <c r="AB10" t="str">
-        <v/>
+        <v>about 0.3°C</v>
       </c>
       <c r="AC10" t="str">
-        <v/>
+        <v>about 1.1°C</v>
       </c>
       <c r="AD10" t="str">
-        <v/>
+        <v>about 3°C</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
+      <c r="B11">
+        <v>3</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>Který zdroj energie celosvětově nejrychleji roste mezi obnovitelnými zdroji?</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>vodní energie</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>geotermální energie</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>solární energie</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>Ktorý zdroj energie celosvetovo najrýchlejšie rastie medzi obnoviteľnými zdrojmi?</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>vodná energia</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>geotermálna energia</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>solárna energia</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>Które źródło energii najszybciej rośnie na świecie wśród źródeł odnawialnych?</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>energia wodna</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>energia geotermalna</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>energia słoneczna</v>
       </c>
       <c r="O11" t="str">
-        <v/>
+        <v>Melyik energiaforrás növekszik leggyorsabban a megújulók között világszerte?</v>
       </c>
       <c r="P11" t="str">
-        <v/>
+        <v>vízenergia</v>
       </c>
       <c r="Q11" t="str">
-        <v/>
+        <v>geotermikus energia</v>
       </c>
       <c r="R11" t="str">
-        <v/>
+        <v>napenergia</v>
       </c>
       <c r="S11" t="str">
-        <v/>
+        <v>Care sursă de energie crește cel mai rapid la nivel mondial în rândul celor regenerabile?</v>
       </c>
       <c r="T11" t="str">
-        <v/>
+        <v>energia hidro</v>
       </c>
       <c r="U11" t="str">
-        <v/>
+        <v>energia geotermală</v>
       </c>
       <c r="V11" t="str">
-        <v/>
+        <v>energia solară</v>
       </c>
       <c r="W11" t="str">
-        <v/>
+        <v>Кой енергиен източник расте най-бързо в световен мащаб сред възобновяемите източници?</v>
       </c>
       <c r="X11" t="str">
-        <v/>
+        <v>водна енергия</v>
       </c>
       <c r="Y11" t="str">
-        <v/>
+        <v>геотермална енергия</v>
       </c>
       <c r="Z11" t="str">
-        <v/>
+        <v>слънчева енергия</v>
       </c>
       <c r="AA11" t="str">
-        <v/>
+        <v>Which energy source is the fastest-growing renewable worldwide?</v>
       </c>
       <c r="AB11" t="str">
-        <v/>
+        <v>hydropower</v>
       </c>
       <c r="AC11" t="str">
-        <v/>
+        <v>geothermal energy</v>
       </c>
       <c r="AD11" t="str">
-        <v/>
+        <v>solar energy</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" t="str">
-        <v/>
+      <c r="B12">
+        <v>1</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>Kolik procent veškeré sladké vody na Zemi je uzamčeno v ledovcích a sněhu?</v>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>cca 70 %</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>cca 2 %</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>cca 20 %</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>Koľko percent všetkej sladkej vody na Zemi je uzamknutých v ľadovcoch a snehu?</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>asi 70 %</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>asi 2 %</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>asi 20 %</v>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>Jaki procent całej słodkiej wody na Ziemi jest uwięziony w lodowcach i śniegu?</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>ok. 70%</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>ok. 2%</v>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>ok. 20%</v>
       </c>
       <c r="O12" t="str">
-        <v/>
+        <v>A Föld édesvízkészletének hány százaléka van jégsapkákban és hóban megkötve?</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>kb. 70%-a</v>
       </c>
       <c r="Q12" t="str">
-        <v/>
+        <v>kb. 2%-a</v>
       </c>
       <c r="R12" t="str">
-        <v/>
+        <v>kb. 20%-a</v>
       </c>
       <c r="S12" t="str">
-        <v/>
+        <v>Ce procent din toată apa dulce a Pământului este blocat în calote de gheață și zăpadă?</v>
       </c>
       <c r="T12" t="str">
-        <v/>
+        <v>aprox. 70%</v>
       </c>
       <c r="U12" t="str">
-        <v/>
+        <v>aprox. 2%</v>
       </c>
       <c r="V12" t="str">
-        <v/>
+        <v>aprox. 20%</v>
       </c>
       <c r="W12" t="str">
-        <v/>
+        <v>Какъв процент от прясната вода на Земята е заключен в ледени шапки и сняг?</v>
       </c>
       <c r="X12" t="str">
-        <v/>
+        <v>около 70%</v>
       </c>
       <c r="Y12" t="str">
-        <v/>
+        <v>около 2%</v>
       </c>
       <c r="Z12" t="str">
-        <v/>
+        <v>около 20%</v>
       </c>
       <c r="AA12" t="str">
-        <v/>
+        <v>What percentage of all Earth's fresh water is locked up in ice caps and snow?</v>
       </c>
       <c r="AB12" t="str">
-        <v/>
+        <v>about 70%</v>
       </c>
       <c r="AC12" t="str">
-        <v/>
+        <v>about 2%</v>
       </c>
       <c r="AD12" t="str">
-        <v/>
+        <v>about 20%</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>Jaký je typický dojezd moderního elektromobilu na jedno nabití?</v>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>cca 50 km</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>cca 300–400 km</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>cca 1000 km</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>Aký je typický dojazd moderného elektromobilu na jedno nabitie?</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>asi 50 km</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>asi 300 – 400 km</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>asi 1000 km</v>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>Jaki jest typowy zasięg nowoczesnego samochodu elektrycznego na jednym ładowaniu?</v>
       </c>
       <c r="L13" t="str">
-        <v/>
+        <v>ok. 50 km</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>ok. 300–400 km</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>ok. 1000 km</v>
       </c>
       <c r="O13" t="str">
-        <v/>
+        <v>Mekkora egy modern elektromos autó jellemző hatótávolsága egy feltöltéssel?</v>
       </c>
       <c r="P13" t="str">
-        <v/>
+        <v>kb. 50 km</v>
       </c>
       <c r="Q13" t="str">
-        <v/>
+        <v>kb. 300–400 km</v>
       </c>
       <c r="R13" t="str">
-        <v/>
+        <v>kb. 1000 km</v>
       </c>
       <c r="S13" t="str">
-        <v/>
+        <v>Care este autonomia tipică a unei mașini electrice moderne la o singură încărcare?</v>
       </c>
       <c r="T13" t="str">
-        <v/>
+        <v>aprox. 50 km</v>
       </c>
       <c r="U13" t="str">
-        <v/>
+        <v>aprox. 300–400 km</v>
       </c>
       <c r="V13" t="str">
-        <v/>
+        <v>aprox. 1000 km</v>
       </c>
       <c r="W13" t="str">
-        <v/>
+        <v>Какъв е типичният пробег на съвременен електромобил с едно зареждане?</v>
       </c>
       <c r="X13" t="str">
-        <v/>
+        <v>около 50 км</v>
       </c>
       <c r="Y13" t="str">
-        <v/>
+        <v>около 300–400 км</v>
       </c>
       <c r="Z13" t="str">
-        <v/>
+        <v>около 1000 км</v>
       </c>
       <c r="AA13" t="str">
-        <v/>
+        <v>What's the typical range of a modern electric car on a single charge?</v>
       </c>
       <c r="AB13" t="str">
-        <v/>
+        <v>about 50 km</v>
       </c>
       <c r="AC13" t="str">
-        <v/>
+        <v>about 300–400 km</v>
       </c>
       <c r="AD13" t="str">
-        <v/>
+        <v>about 1,000 km</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" t="str">
-        <v/>
+      <c r="B14">
+        <v>3</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>Kolik druhů rostlin a živočichů podle odhadů ročně vymírá kvůli lidské činnosti?</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>desítky</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>statisíce</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>tisíce</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>Koľko druhov rastlín a živočíchov podľa odhadov ročne vyhynie v dôsledku ľudskej činnosti?</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>desiatky</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>stotisíce</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>tisíce</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>Ile gatunków roślin i zwierząt szacunkowo wymiera rocznie z powodu działalności człowieka?</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>dziesiątki</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>setki tysięcy</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>tysiące</v>
       </c>
       <c r="O14" t="str">
-        <v/>
+        <v>Becslések szerint hány növény- és állatfaj hal ki évente az emberi tevékenység miatt?</v>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>tucatnyi</v>
       </c>
       <c r="Q14" t="str">
-        <v/>
+        <v>több százezer</v>
       </c>
       <c r="R14" t="str">
-        <v/>
+        <v>több ezer</v>
       </c>
       <c r="S14" t="str">
-        <v/>
+        <v>Aproximativ câte specii de plante și animale se estimează că dispar anual din cauza activității umane?</v>
       </c>
       <c r="T14" t="str">
-        <v/>
+        <v>zeci</v>
       </c>
       <c r="U14" t="str">
-        <v/>
+        <v>sute de mii</v>
       </c>
       <c r="V14" t="str">
-        <v/>
+        <v>mii</v>
       </c>
       <c r="W14" t="str">
-        <v/>
+        <v>Приблизително колко видове растения и животни се смята, че изчезват годишно поради човешка дейност?</v>
       </c>
       <c r="X14" t="str">
-        <v/>
+        <v>десетки</v>
       </c>
       <c r="Y14" t="str">
-        <v/>
+        <v>стотици хиляди</v>
       </c>
       <c r="Z14" t="str">
-        <v/>
+        <v>хиляди</v>
       </c>
       <c r="AA14" t="str">
-        <v/>
+        <v>Roughly how many plant and animal species are estimated to go extinct each year due to human activity?</v>
       </c>
       <c r="AB14" t="str">
-        <v/>
+        <v>dozens</v>
       </c>
       <c r="AC14" t="str">
-        <v/>
+        <v>hundreds of thousands</v>
       </c>
       <c r="AD14" t="str">
-        <v/>
+        <v>thousands</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" t="str">
-        <v/>
+      <c r="B15">
+        <v>1</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>Jaký je celosvětově hlavní zdroj emisí skleníkových plynů?</v>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>spalování fosilních paliv na energii</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>doprava</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>zemědělství</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>Čo je celosvetovo najväčším zdrojom emisií skleníkových plynov?</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>spaľovanie fosílnych palív na energiu</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>doprava</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>poľnohospodárstvo</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>Co jest największym źródłem emisji gazów cieplarnianych na świecie?</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>spalanie paliw kopalnych do produkcji energii</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>transport</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>rolnictwo</v>
       </c>
       <c r="O15" t="str">
-        <v/>
+        <v>Mi világszerte az üvegházhatású gázok kibocsátásának legnagyobb forrása?</v>
       </c>
       <c r="P15" t="str">
-        <v/>
+        <v>fosszilis tüzelőanyagok elégetése energiatermelésre</v>
       </c>
       <c r="Q15" t="str">
-        <v/>
+        <v>közlekedés</v>
       </c>
       <c r="R15" t="str">
-        <v/>
+        <v>mezőgazdaság</v>
       </c>
       <c r="S15" t="str">
-        <v/>
+        <v>Care este cea mai mare sursă de emisii de gaze cu efect de seră la nivel mondial?</v>
       </c>
       <c r="T15" t="str">
-        <v/>
+        <v>arderea combustibililor fosili pentru energie</v>
       </c>
       <c r="U15" t="str">
-        <v/>
+        <v>transportul</v>
       </c>
       <c r="V15" t="str">
-        <v/>
+        <v>agricultura</v>
       </c>
       <c r="W15" t="str">
-        <v/>
+        <v>Кой е най-големият източник на емисии на парникови газове в световен мащаб?</v>
       </c>
       <c r="X15" t="str">
-        <v/>
+        <v>изгаряне на изкопаеми горива за енергия</v>
       </c>
       <c r="Y15" t="str">
-        <v/>
+        <v>транспорт</v>
       </c>
       <c r="Z15" t="str">
-        <v/>
+        <v>земеделие</v>
       </c>
       <c r="AA15" t="str">
-        <v/>
+        <v>What is the biggest source of greenhouse gas emissions worldwide?</v>
       </c>
       <c r="AB15" t="str">
-        <v/>
+        <v>burning fossil fuels for energy</v>
       </c>
       <c r="AC15" t="str">
-        <v/>
+        <v>transport</v>
       </c>
       <c r="AD15" t="str">
-        <v/>
+        <v>agriculture</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" t="str">
-        <v/>
+      <c r="B16">
+        <v>2</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>Kolik procent vyrobených potravin se celosvětově vyplýtvá nebo znehodnotí, než se sní?</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>cca 5 %</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>cca 33 %</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>cca 70 %</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>Koľko percent vyrobených potravín sa celosvetovo vyplytvá alebo znehodnotí, kým sa zjedia?</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>asi 5 %</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>asi 33 %</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>asi 70 %</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>Jaki procent wyprodukowanej żywności na świecie jest marnowany, zanim zostanie zjedzony?</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>ok. 5%</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>ok. 33%</v>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>ok. 70%</v>
       </c>
       <c r="O16" t="str">
-        <v/>
+        <v>A megtermelt élelmiszer hány százaléka megy veszendőbe vagy romlik meg világszerte, mielőtt elfogyasztanák?</v>
       </c>
       <c r="P16" t="str">
-        <v/>
+        <v>kb. 5%-a</v>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>kb. 33%-a</v>
       </c>
       <c r="R16" t="str">
-        <v/>
+        <v>kb. 70%-a</v>
       </c>
       <c r="S16" t="str">
-        <v/>
+        <v>Ce procent din alimentele produse la nivel mondial este irosit sau se strică înainte de a fi consumat?</v>
       </c>
       <c r="T16" t="str">
-        <v/>
+        <v>aprox. 5%</v>
       </c>
       <c r="U16" t="str">
-        <v/>
+        <v>aprox. 33%</v>
       </c>
       <c r="V16" t="str">
-        <v/>
+        <v>aprox. 70%</v>
       </c>
       <c r="W16" t="str">
-        <v/>
+        <v>Какъв процент от произведената в света храна се разхищава или разваля, преди да бъде изядена?</v>
       </c>
       <c r="X16" t="str">
-        <v/>
+        <v>около 5%</v>
       </c>
       <c r="Y16" t="str">
-        <v/>
+        <v>около 33%</v>
       </c>
       <c r="Z16" t="str">
-        <v/>
+        <v>около 70%</v>
       </c>
       <c r="AA16" t="str">
-        <v/>
+        <v>What percentage of food produced worldwide is wasted or lost before it's eaten?</v>
       </c>
       <c r="AB16" t="str">
-        <v/>
+        <v>about 5%</v>
       </c>
       <c r="AC16" t="str">
-        <v/>
+        <v>about 33%</v>
       </c>
       <c r="AD16" t="str">
-        <v/>
+        <v>about 70%</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" t="str">
-        <v/>
+      <c r="B17">
+        <v>3</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>Jak dlouho trvá, než se v přírodě rozloží cigaretový nedopalek?</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>pár dní</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>1–2 roky</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>10–12 let</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>Ako dlho trvá, kým sa v prírode rozloží ohorok z cigarety?</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>pár dní</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>1 – 2 roky</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>10 – 12 rokov</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>Ile czasu zajmuje rozkład niedopałka papierosa w przyrodzie?</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>kilka dni</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>1–2 lata</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>10–12 lat</v>
       </c>
       <c r="O17" t="str">
-        <v/>
+        <v>Mennyi idő alatt bomlik le a természetben egy cigarettacsikk?</v>
       </c>
       <c r="P17" t="str">
-        <v/>
+        <v>néhány nap</v>
       </c>
       <c r="Q17" t="str">
-        <v/>
+        <v>1–2 év</v>
       </c>
       <c r="R17" t="str">
-        <v/>
+        <v>10–12 év</v>
       </c>
       <c r="S17" t="str">
-        <v/>
+        <v>Cât timp durează până când un muc de țigară se descompune în natură?</v>
       </c>
       <c r="T17" t="str">
-        <v/>
+        <v>câteva zile</v>
       </c>
       <c r="U17" t="str">
-        <v/>
+        <v>1–2 ani</v>
       </c>
       <c r="V17" t="str">
-        <v/>
+        <v>10–12 ani</v>
       </c>
       <c r="W17" t="str">
-        <v/>
+        <v>Колко време отнема разграждането на фас от цигара в природата?</v>
       </c>
       <c r="X17" t="str">
-        <v/>
+        <v>няколко дни</v>
       </c>
       <c r="Y17" t="str">
-        <v/>
+        <v>1–2 години</v>
       </c>
       <c r="Z17" t="str">
-        <v/>
+        <v>10–12 години</v>
       </c>
       <c r="AA17" t="str">
-        <v/>
+        <v>How long does it take a cigarette butt to decompose in nature?</v>
       </c>
       <c r="AB17" t="str">
-        <v/>
+        <v>a few days</v>
       </c>
       <c r="AC17" t="str">
-        <v/>
+        <v>1–2 years</v>
       </c>
       <c r="AD17" t="str">
-        <v/>
+        <v>10–12 years</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" t="str">
-        <v/>
+      <c r="B18">
+        <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>Kolik procent elektřiny se v posledních letech celosvětově vyrábí z obnovitelných zdrojů?</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>cca 30 %</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>cca 5 %</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>cca 60 %</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>Koľko percent elektriny sa v posledných rokoch celosvetovo vyrába z obnoviteľných zdrojov?</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>asi 30 %</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>asi 5 %</v>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>asi 60 %</v>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>Jaki procent światowej energii elektrycznej pochodzi ostatnio ze źródeł odnawialnych?</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>ok. 30%</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>ok. 5%</v>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>ok. 60%</v>
       </c>
       <c r="O18" t="str">
-        <v/>
+        <v>A világ villamosenergia-termelésének hány százaléka származott az utóbbi években megújuló forrásokból?</v>
       </c>
       <c r="P18" t="str">
-        <v/>
+        <v>kb. 30%-a</v>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>kb. 5%-a</v>
       </c>
       <c r="R18" t="str">
-        <v/>
+        <v>kb. 60%-a</v>
       </c>
       <c r="S18" t="str">
-        <v/>
+        <v>Ce pondere din energia electrică produsă la nivel mondial a provenit recent din surse regenerabile?</v>
       </c>
       <c r="T18" t="str">
-        <v/>
+        <v>aprox. 30%</v>
       </c>
       <c r="U18" t="str">
-        <v/>
+        <v>aprox. 5%</v>
       </c>
       <c r="V18" t="str">
-        <v/>
+        <v>aprox. 60%</v>
       </c>
       <c r="W18" t="str">
-        <v/>
+        <v>Какъв дял от електроенергията в света през последните години се произвежда от възобновяеми източници?</v>
       </c>
       <c r="X18" t="str">
-        <v/>
+        <v>около 30%</v>
       </c>
       <c r="Y18" t="str">
-        <v/>
+        <v>около 5%</v>
       </c>
       <c r="Z18" t="str">
-        <v/>
+        <v>около 60%</v>
       </c>
       <c r="AA18" t="str">
-        <v/>
+        <v>What share of the world's electricity has recently been generated from renewable sources?</v>
       </c>
       <c r="AB18" t="str">
-        <v/>
+        <v>about 30%</v>
       </c>
       <c r="AC18" t="str">
-        <v/>
+        <v>about 5%</v>
       </c>
       <c r="AD18" t="str">
-        <v/>
+        <v>about 60%</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" t="str">
-        <v/>
+      <c r="B19">
+        <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>Který dopravní prostředek má na kilometr a osobu nejnižší uhlíkovou stopu?</v>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>osobní auto</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>vlak</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>letadlo</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>Ktorý dopravný prostriedok má na kilometer a osobu najnižšiu uhlíkovú stopu?</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>osobné auto</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>vlak</v>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>lietadlo</v>
       </c>
       <c r="K19" t="str">
-        <v/>
+        <v>Który środek transportu ma najniższy ślad węglowy na kilometr na osobę?</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>samochód osobowy</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>pociąg</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>samolot</v>
       </c>
       <c r="O19" t="str">
-        <v/>
+        <v>Melyik közlekedési eszköznek a legalacsonyabb a szén-dioxid-lábnyoma személy- és kilométerenként?</v>
       </c>
       <c r="P19" t="str">
-        <v/>
+        <v>személygépkocsi</v>
       </c>
       <c r="Q19" t="str">
-        <v/>
+        <v>vonat</v>
       </c>
       <c r="R19" t="str">
-        <v/>
+        <v>repülőgép</v>
       </c>
       <c r="S19" t="str">
-        <v/>
+        <v>Care mijloc de transport are cea mai mică amprentă de carbon pe persoană și kilometru?</v>
       </c>
       <c r="T19" t="str">
-        <v/>
+        <v>mașina personală</v>
       </c>
       <c r="U19" t="str">
-        <v/>
+        <v>trenul</v>
       </c>
       <c r="V19" t="str">
-        <v/>
+        <v>avionul</v>
       </c>
       <c r="W19" t="str">
-        <v/>
+        <v>Кое превозно средство има най-нисък въглероден отпечатък на километър на човек?</v>
       </c>
       <c r="X19" t="str">
-        <v/>
+        <v>лек автомобил</v>
       </c>
       <c r="Y19" t="str">
-        <v/>
+        <v>влак</v>
       </c>
       <c r="Z19" t="str">
-        <v/>
+        <v>самолет</v>
       </c>
       <c r="AA19" t="str">
-        <v/>
+        <v>Which mode of transport has the lowest carbon footprint per person per kilometre?</v>
       </c>
       <c r="AB19" t="str">
-        <v/>
+        <v>car</v>
       </c>
       <c r="AC19" t="str">
-        <v/>
+        <v>train</v>
       </c>
       <c r="AD19" t="str">
-        <v/>
+        <v>airplane</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" t="str">
-        <v/>
+      <c r="B20">
+        <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>Kolik let trvá, než po vykácení naroste nový les srovnatelný s tím původním?</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>cca 10 let</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>cca 500 let</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>cca 50–100 let</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>Koľko rokov trvá, kým po vyrúbaní dorastie nový les porovnateľný s pôvodným?</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>asi 10 rokov</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>asi 500 rokov</v>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>asi 50 – 100 rokov</v>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>Ile lat zajmuje odrośnięcie nowego lasu porównywalnego z pierwotnym po wycince?</v>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>ok. 10 lat</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>ok. 500 lat</v>
       </c>
       <c r="N20" t="str">
-        <v/>
+        <v>ok. 50–100 lat</v>
       </c>
       <c r="O20" t="str">
-        <v/>
+        <v>Hány évbe telik, míg a kivágás után az eredetihez hasonló új erdő nő vissza?</v>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>kb. 10 évbe</v>
       </c>
       <c r="Q20" t="str">
-        <v/>
+        <v>kb. 500 évbe</v>
       </c>
       <c r="R20" t="str">
-        <v/>
+        <v>kb. 50–100 évbe</v>
       </c>
       <c r="S20" t="str">
-        <v/>
+        <v>Câți ani durează până când o pădure nouă crește la un nivel comparabil cu cea originală după defrișare?</v>
       </c>
       <c r="T20" t="str">
-        <v/>
+        <v>aprox. 10 ani</v>
       </c>
       <c r="U20" t="str">
-        <v/>
+        <v>aprox. 500 de ani</v>
       </c>
       <c r="V20" t="str">
-        <v/>
+        <v>aprox. 50–100 de ani</v>
       </c>
       <c r="W20" t="str">
-        <v/>
+        <v>Колко години отнема нова гора да порасне до състояние, сравнимо с оригиналната, след изсичане?</v>
       </c>
       <c r="X20" t="str">
-        <v/>
+        <v>около 10 години</v>
       </c>
       <c r="Y20" t="str">
-        <v/>
+        <v>около 500 години</v>
       </c>
       <c r="Z20" t="str">
-        <v/>
+        <v>около 50–100 години</v>
       </c>
       <c r="AA20" t="str">
-        <v/>
+        <v>How many years does it take for a new forest to grow back to a state comparable to the original after logging?</v>
       </c>
       <c r="AB20" t="str">
-        <v/>
+        <v>about 10 years</v>
       </c>
       <c r="AC20" t="str">
-        <v/>
+        <v>about 500 years</v>
       </c>
       <c r="AD20" t="str">
-        <v/>
+        <v>about 50–100 years</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" t="str">
-        <v/>
+      <c r="B21">
+        <v>1</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>Kolik odpadu vyprodukuje v průměru jeden Evropan za rok?</v>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>cca 500 kg</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>cca 50 kg</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>cca 2000 kg</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>Koľko odpadu v priemere vyprodukuje jeden Európan za rok?</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>asi 500 kg</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>asi 50 kg</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>asi 2000 kg</v>
       </c>
       <c r="K21" t="str">
-        <v/>
+        <v>Ile odpadów produkuje średnio jeden Europejczyk rocznie?</v>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>ok. 500 kg</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>ok. 50 kg</v>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>ok. 2000 kg</v>
       </c>
       <c r="O21" t="str">
-        <v/>
+        <v>Átlagosan mennyi hulladékot termel egy európai ember évente?</v>
       </c>
       <c r="P21" t="str">
-        <v/>
+        <v>kb. 500 kg-ot</v>
       </c>
       <c r="Q21" t="str">
-        <v/>
+        <v>kb. 50 kg-ot</v>
       </c>
       <c r="R21" t="str">
-        <v/>
+        <v>kb. 2000 kg-ot</v>
       </c>
       <c r="S21" t="str">
-        <v/>
+        <v>Câte deșeuri produce, în medie, un european pe an?</v>
       </c>
       <c r="T21" t="str">
-        <v/>
+        <v>aprox. 500 kg</v>
       </c>
       <c r="U21" t="str">
-        <v/>
+        <v>aprox. 50 kg</v>
       </c>
       <c r="V21" t="str">
-        <v/>
+        <v>aprox. 2000 kg</v>
       </c>
       <c r="W21" t="str">
-        <v/>
+        <v>Средно колко отпадъци произвежда един европеец годишно?</v>
       </c>
       <c r="X21" t="str">
-        <v/>
+        <v>около 500 кг</v>
       </c>
       <c r="Y21" t="str">
-        <v/>
+        <v>около 50 кг</v>
       </c>
       <c r="Z21" t="str">
-        <v/>
+        <v>около 2000 кг</v>
       </c>
       <c r="AA21" t="str">
-        <v/>
+        <v>How much waste does the average European produce per year?</v>
       </c>
       <c r="AB21" t="str">
-        <v/>
+        <v>about 500 kg</v>
       </c>
       <c r="AC21" t="str">
-        <v/>
+        <v>about 50 kg</v>
       </c>
       <c r="AD21" t="str">
-        <v/>
+        <v>about 2,000 kg</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" t="str">
-        <v/>
+      <c r="B22">
+        <v>2</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>Co znamená zkratka „ESG“, často zmiňovaná v souvislosti s udržitelností firem?</v>
       </c>
       <c r="D22" t="str">
-        <v/>
+        <v>Energy, Science, Growth</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>Environmental, Social, Governance</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>Efficiency, Sustainability, Goals</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>Čo znamená skratka „ESG“, často spomínaná v súvislosti s udržateľnosťou firiem?</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>Energy, Science, Growth</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>Environmental, Social, Governance</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>Efficiency, Sustainability, Goals</v>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>Co oznacza skrót „ESG”, często wspominany w kontekście zrównoważonego rozwoju firm?</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>Energy, Science, Growth</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>Environmental, Social, Governance</v>
       </c>
       <c r="N22" t="str">
-        <v/>
+        <v>Efficiency, Sustainability, Goals</v>
       </c>
       <c r="O22" t="str">
-        <v/>
+        <v>Mit jelent az „ESG” rövidítés, amelyet gyakran említenek a vállalati fenntarthatósággal kapcsolatban?</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>Energy, Science, Growth</v>
       </c>
       <c r="Q22" t="str">
-        <v/>
+        <v>Environmental, Social, Governance</v>
       </c>
       <c r="R22" t="str">
-        <v/>
+        <v>Efficiency, Sustainability, Goals</v>
       </c>
       <c r="S22" t="str">
-        <v/>
+        <v>Ce înseamnă abrevierea „ESG”, des menționată în legătură cu sustenabilitatea companiilor?</v>
       </c>
       <c r="T22" t="str">
-        <v/>
+        <v>Energy, Science, Growth</v>
       </c>
       <c r="U22" t="str">
-        <v/>
+        <v>Environmental, Social, Governance</v>
       </c>
       <c r="V22" t="str">
-        <v/>
+        <v>Efficiency, Sustainability, Goals</v>
       </c>
       <c r="W22" t="str">
-        <v/>
+        <v>Какво означава съкращението „ESG“, често споменавано във връзка с устойчивостта на компаниите?</v>
       </c>
       <c r="X22" t="str">
-        <v/>
+        <v>Energy, Science, Growth</v>
       </c>
       <c r="Y22" t="str">
-        <v/>
+        <v>Environmental, Social, Governance</v>
       </c>
       <c r="Z22" t="str">
-        <v/>
+        <v>Efficiency, Sustainability, Goals</v>
       </c>
       <c r="AA22" t="str">
-        <v/>
+        <v>What does the abbreviation "ESG", often mentioned in relation to corporate sustainability, stand for?</v>
       </c>
       <c r="AB22" t="str">
-        <v/>
+        <v>Energy, Science, Growth</v>
       </c>
       <c r="AC22" t="str">
-        <v/>
+        <v>Environmental, Social, Governance</v>
       </c>
       <c r="AD22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23" t="str">
-        <v/>
-      </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <v/>
-      </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <v/>
-      </c>
-      <c r="P23" t="str">
-        <v/>
-      </c>
-      <c r="Q23" t="str">
-        <v/>
-      </c>
-      <c r="R23" t="str">
-        <v/>
-      </c>
-      <c r="S23" t="str">
-        <v/>
-      </c>
-      <c r="T23" t="str">
-        <v/>
-      </c>
-      <c r="U23" t="str">
-        <v/>
-      </c>
-      <c r="V23" t="str">
-        <v/>
-      </c>
-      <c r="W23" t="str">
-        <v/>
-      </c>
-      <c r="X23" t="str">
-        <v/>
-      </c>
-      <c r="Y23" t="str">
-        <v/>
-      </c>
-      <c r="Z23" t="str">
-        <v/>
-      </c>
-      <c r="AA23" t="str">
-        <v/>
-      </c>
-      <c r="AB23" t="str">
-        <v/>
-      </c>
-      <c r="AC23" t="str">
-        <v/>
-      </c>
-      <c r="AD23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24" t="str">
-        <v/>
-      </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-      <c r="P24" t="str">
-        <v/>
-      </c>
-      <c r="Q24" t="str">
-        <v/>
-      </c>
-      <c r="R24" t="str">
-        <v/>
-      </c>
-      <c r="S24" t="str">
-        <v/>
-      </c>
-      <c r="T24" t="str">
-        <v/>
-      </c>
-      <c r="U24" t="str">
-        <v/>
-      </c>
-      <c r="V24" t="str">
-        <v/>
-      </c>
-      <c r="W24" t="str">
-        <v/>
-      </c>
-      <c r="X24" t="str">
-        <v/>
-      </c>
-      <c r="Y24" t="str">
-        <v/>
-      </c>
-      <c r="Z24" t="str">
-        <v/>
-      </c>
-      <c r="AA24" t="str">
-        <v/>
-      </c>
-      <c r="AB24" t="str">
-        <v/>
-      </c>
-      <c r="AC24" t="str">
-        <v/>
-      </c>
-      <c r="AD24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25" t="str">
-        <v/>
-      </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25" t="str">
-        <v/>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-      <c r="P25" t="str">
-        <v/>
-      </c>
-      <c r="Q25" t="str">
-        <v/>
-      </c>
-      <c r="R25" t="str">
-        <v/>
-      </c>
-      <c r="S25" t="str">
-        <v/>
-      </c>
-      <c r="T25" t="str">
-        <v/>
-      </c>
-      <c r="U25" t="str">
-        <v/>
-      </c>
-      <c r="V25" t="str">
-        <v/>
-      </c>
-      <c r="W25" t="str">
-        <v/>
-      </c>
-      <c r="X25" t="str">
-        <v/>
-      </c>
-      <c r="Y25" t="str">
-        <v/>
-      </c>
-      <c r="Z25" t="str">
-        <v/>
-      </c>
-      <c r="AA25" t="str">
-        <v/>
-      </c>
-      <c r="AB25" t="str">
-        <v/>
-      </c>
-      <c r="AC25" t="str">
-        <v/>
-      </c>
-      <c r="AD25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26" t="str">
-        <v/>
-      </c>
-      <c r="C26" t="str">
-        <v/>
-      </c>
-      <c r="D26" t="str">
-        <v/>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-      <c r="Q26" t="str">
-        <v/>
-      </c>
-      <c r="R26" t="str">
-        <v/>
-      </c>
-      <c r="S26" t="str">
-        <v/>
-      </c>
-      <c r="T26" t="str">
-        <v/>
-      </c>
-      <c r="U26" t="str">
-        <v/>
-      </c>
-      <c r="V26" t="str">
-        <v/>
-      </c>
-      <c r="W26" t="str">
-        <v/>
-      </c>
-      <c r="X26" t="str">
-        <v/>
-      </c>
-      <c r="Y26" t="str">
-        <v/>
-      </c>
-      <c r="Z26" t="str">
-        <v/>
-      </c>
-      <c r="AA26" t="str">
-        <v/>
-      </c>
-      <c r="AB26" t="str">
-        <v/>
-      </c>
-      <c r="AC26" t="str">
-        <v/>
-      </c>
-      <c r="AD26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27" t="str">
-        <v/>
-      </c>
-      <c r="C27" t="str">
-        <v/>
-      </c>
-      <c r="D27" t="str">
-        <v/>
-      </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-      <c r="F27" t="str">
-        <v/>
-      </c>
-      <c r="G27" t="str">
-        <v/>
-      </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
-      <c r="N27" t="str">
-        <v/>
-      </c>
-      <c r="O27" t="str">
-        <v/>
-      </c>
-      <c r="P27" t="str">
-        <v/>
-      </c>
-      <c r="Q27" t="str">
-        <v/>
-      </c>
-      <c r="R27" t="str">
-        <v/>
-      </c>
-      <c r="S27" t="str">
-        <v/>
-      </c>
-      <c r="T27" t="str">
-        <v/>
-      </c>
-      <c r="U27" t="str">
-        <v/>
-      </c>
-      <c r="V27" t="str">
-        <v/>
-      </c>
-      <c r="W27" t="str">
-        <v/>
-      </c>
-      <c r="X27" t="str">
-        <v/>
-      </c>
-      <c r="Y27" t="str">
-        <v/>
-      </c>
-      <c r="Z27" t="str">
-        <v/>
-      </c>
-      <c r="AA27" t="str">
-        <v/>
-      </c>
-      <c r="AB27" t="str">
-        <v/>
-      </c>
-      <c r="AC27" t="str">
-        <v/>
-      </c>
-      <c r="AD27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28" t="str">
-        <v/>
-      </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-      <c r="F28" t="str">
-        <v/>
-      </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="J28" t="str">
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v/>
-      </c>
-      <c r="M28" t="str">
-        <v/>
-      </c>
-      <c r="N28" t="str">
-        <v/>
-      </c>
-      <c r="O28" t="str">
-        <v/>
-      </c>
-      <c r="P28" t="str">
-        <v/>
-      </c>
-      <c r="Q28" t="str">
-        <v/>
-      </c>
-      <c r="R28" t="str">
-        <v/>
-      </c>
-      <c r="S28" t="str">
-        <v/>
-      </c>
-      <c r="T28" t="str">
-        <v/>
-      </c>
-      <c r="U28" t="str">
-        <v/>
-      </c>
-      <c r="V28" t="str">
-        <v/>
-      </c>
-      <c r="W28" t="str">
-        <v/>
-      </c>
-      <c r="X28" t="str">
-        <v/>
-      </c>
-      <c r="Y28" t="str">
-        <v/>
-      </c>
-      <c r="Z28" t="str">
-        <v/>
-      </c>
-      <c r="AA28" t="str">
-        <v/>
-      </c>
-      <c r="AB28" t="str">
-        <v/>
-      </c>
-      <c r="AC28" t="str">
-        <v/>
-      </c>
-      <c r="AD28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29" t="str">
-        <v/>
-      </c>
-      <c r="C29" t="str">
-        <v/>
-      </c>
-      <c r="D29" t="str">
-        <v/>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29" t="str">
-        <v/>
-      </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
-      <c r="J29" t="str">
-        <v/>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
-      <c r="N29" t="str">
-        <v/>
-      </c>
-      <c r="O29" t="str">
-        <v/>
-      </c>
-      <c r="P29" t="str">
-        <v/>
-      </c>
-      <c r="Q29" t="str">
-        <v/>
-      </c>
-      <c r="R29" t="str">
-        <v/>
-      </c>
-      <c r="S29" t="str">
-        <v/>
-      </c>
-      <c r="T29" t="str">
-        <v/>
-      </c>
-      <c r="U29" t="str">
-        <v/>
-      </c>
-      <c r="V29" t="str">
-        <v/>
-      </c>
-      <c r="W29" t="str">
-        <v/>
-      </c>
-      <c r="X29" t="str">
-        <v/>
-      </c>
-      <c r="Y29" t="str">
-        <v/>
-      </c>
-      <c r="Z29" t="str">
-        <v/>
-      </c>
-      <c r="AA29" t="str">
-        <v/>
-      </c>
-      <c r="AB29" t="str">
-        <v/>
-      </c>
-      <c r="AC29" t="str">
-        <v/>
-      </c>
-      <c r="AD29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30" t="str">
-        <v/>
-      </c>
-      <c r="C30" t="str">
-        <v/>
-      </c>
-      <c r="D30" t="str">
-        <v/>
-      </c>
-      <c r="E30" t="str">
-        <v/>
-      </c>
-      <c r="F30" t="str">
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <v/>
-      </c>
-      <c r="H30" t="str">
-        <v/>
-      </c>
-      <c r="I30" t="str">
-        <v/>
-      </c>
-      <c r="J30" t="str">
-        <v/>
-      </c>
-      <c r="K30" t="str">
-        <v/>
-      </c>
-      <c r="L30" t="str">
-        <v/>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-      <c r="N30" t="str">
-        <v/>
-      </c>
-      <c r="O30" t="str">
-        <v/>
-      </c>
-      <c r="P30" t="str">
-        <v/>
-      </c>
-      <c r="Q30" t="str">
-        <v/>
-      </c>
-      <c r="R30" t="str">
-        <v/>
-      </c>
-      <c r="S30" t="str">
-        <v/>
-      </c>
-      <c r="T30" t="str">
-        <v/>
-      </c>
-      <c r="U30" t="str">
-        <v/>
-      </c>
-      <c r="V30" t="str">
-        <v/>
-      </c>
-      <c r="W30" t="str">
-        <v/>
-      </c>
-      <c r="X30" t="str">
-        <v/>
-      </c>
-      <c r="Y30" t="str">
-        <v/>
-      </c>
-      <c r="Z30" t="str">
-        <v/>
-      </c>
-      <c r="AA30" t="str">
-        <v/>
-      </c>
-      <c r="AB30" t="str">
-        <v/>
-      </c>
-      <c r="AC30" t="str">
-        <v/>
-      </c>
-      <c r="AD30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31" t="str">
-        <v/>
-      </c>
-      <c r="C31" t="str">
-        <v/>
-      </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
-      <c r="E31" t="str">
-        <v/>
-      </c>
-      <c r="F31" t="str">
-        <v/>
-      </c>
-      <c r="G31" t="str">
-        <v/>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31" t="str">
-        <v/>
-      </c>
-      <c r="J31" t="str">
-        <v/>
-      </c>
-      <c r="K31" t="str">
-        <v/>
-      </c>
-      <c r="L31" t="str">
-        <v/>
-      </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
-      <c r="N31" t="str">
-        <v/>
-      </c>
-      <c r="O31" t="str">
-        <v/>
-      </c>
-      <c r="P31" t="str">
-        <v/>
-      </c>
-      <c r="Q31" t="str">
-        <v/>
-      </c>
-      <c r="R31" t="str">
-        <v/>
-      </c>
-      <c r="S31" t="str">
-        <v/>
-      </c>
-      <c r="T31" t="str">
-        <v/>
-      </c>
-      <c r="U31" t="str">
-        <v/>
-      </c>
-      <c r="V31" t="str">
-        <v/>
-      </c>
-      <c r="W31" t="str">
-        <v/>
-      </c>
-      <c r="X31" t="str">
-        <v/>
-      </c>
-      <c r="Y31" t="str">
-        <v/>
-      </c>
-      <c r="Z31" t="str">
-        <v/>
-      </c>
-      <c r="AA31" t="str">
-        <v/>
-      </c>
-      <c r="AB31" t="str">
-        <v/>
-      </c>
-      <c r="AC31" t="str">
-        <v/>
-      </c>
-      <c r="AD31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="B32" t="str">
-        <v/>
-      </c>
-      <c r="C32" t="str">
-        <v/>
-      </c>
-      <c r="D32" t="str">
-        <v/>
-      </c>
-      <c r="E32" t="str">
-        <v/>
-      </c>
-      <c r="F32" t="str">
-        <v/>
-      </c>
-      <c r="G32" t="str">
-        <v/>
-      </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
-      <c r="I32" t="str">
-        <v/>
-      </c>
-      <c r="J32" t="str">
-        <v/>
-      </c>
-      <c r="K32" t="str">
-        <v/>
-      </c>
-      <c r="L32" t="str">
-        <v/>
-      </c>
-      <c r="M32" t="str">
-        <v/>
-      </c>
-      <c r="N32" t="str">
-        <v/>
-      </c>
-      <c r="O32" t="str">
-        <v/>
-      </c>
-      <c r="P32" t="str">
-        <v/>
-      </c>
-      <c r="Q32" t="str">
-        <v/>
-      </c>
-      <c r="R32" t="str">
-        <v/>
-      </c>
-      <c r="S32" t="str">
-        <v/>
-      </c>
-      <c r="T32" t="str">
-        <v/>
-      </c>
-      <c r="U32" t="str">
-        <v/>
-      </c>
-      <c r="V32" t="str">
-        <v/>
-      </c>
-      <c r="W32" t="str">
-        <v/>
-      </c>
-      <c r="X32" t="str">
-        <v/>
-      </c>
-      <c r="Y32" t="str">
-        <v/>
-      </c>
-      <c r="Z32" t="str">
-        <v/>
-      </c>
-      <c r="AA32" t="str">
-        <v/>
-      </c>
-      <c r="AB32" t="str">
-        <v/>
-      </c>
-      <c r="AC32" t="str">
-        <v/>
-      </c>
-      <c r="AD32" t="str">
-        <v/>
+        <v>Efficiency, Sustainability, Goals</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD22"/>
   </ignoredErrors>
 </worksheet>
 </file>
